--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_953_South_Africa_Atlantic_and_Cape.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_953_South_Africa_Atlantic_and_Cape.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R64759e72b28d4f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1a676b63c7914402"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rcbaf4946bcb94231"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5d0846654ca44288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf96c4b453a904349"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0c5e1eeed7e14d8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R974a9caca36a421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R864af4f2a8fb47dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2335b842b6b2401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1ed530c6245f4df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R241a75e273f84e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R52c8c5153f39498c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ953CommercialTable" displayName="EEZ953CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ953CommercialTable" displayName="EEZ953CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ953FunctionalTable" displayName="EEZ953FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ953FunctionalTable" displayName="EEZ953FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ953ValidationTable" displayName="EEZ953ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ953ValidationTable" displayName="EEZ953ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7394,7 +7348,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd673d1d50b6541b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ff471829b7e4fcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7404,20 +7358,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7425,660 +7369,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>329343.663495</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>329343.663495</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$101,A2,'Species'!$U$2:$U$101))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>32934366.3495</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>32934366.3495</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>146830.607454574</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.287013748275</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1936.4832654002946</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>146830.607454574</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1953.5890350387065</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$101,A3,'Species'!$U$2:$U$101))</x:f>
-        <x:v>286846664.7313283</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.287013748275</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1936.4832654002946</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>284335014.1843423</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2511650.546985984</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.008833419810047</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00883341981004707</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1898.4695828672002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.6159383820294</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>41.298890271140586</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1898.4695828672002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>43.00824038366324</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$101,A4,'Species'!$U$2:$U$101))</x:f>
-        <x:v>81649.83618102543</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.6159383820294</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>41.298890271140586</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>78404.68698593054</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3245.149195094884</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0413897347192678</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.04138973471926768</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>190.13000000000002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.03</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1071.519305237607</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>190.13000000000002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1071.519305237607</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$101,A5,'Species'!$U$2:$U$101))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>203727.96550482628</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.03</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1071.519305237607</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>203727.96550482628</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>52658.72</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3444897407305003</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>221.04960374861705</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>52658.72</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>233.14725913269803</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$101,A6,'Species'!$U$2:$U$101))</x:f>
-        <x:v>12277236.237436188</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3444897407305003</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>221.04960374861705</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>11640189.189909376</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>637047.0475268122</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0547282382728842</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.054728238272884276</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1506.855868496</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0183809829168524</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.432321989365464</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1506.855868496</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.558017593378262</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$101,A7,'Species'!$U$2:$U$101))</x:f>
-        <x:v>15909.41077026605</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0183809829168524</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.432321989365464</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>15720.005611715216</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>189.40515855083322</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.012048669906942</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.012048669906942047</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>44616.50112421</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.788366109083912</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>614.2796230342525</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>44616.50112421</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1212.938978206767</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$101,A8,'Species'!$U$2:$U$101))</x:f>
-        <x:v>54117093.28476035</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.788366109083912</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>614.2796230342525</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>27407007.491687022</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>26710085.793073326</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.974571404819549</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9745714048195491</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>43650.707039625406</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.560238078989383</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>363.2771476844816</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>43650.707039625406</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>452.4883938601915</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$101,A9,'Species'!$U$2:$U$101))</x:f>
-        <x:v>19751438.319221854</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.560238078989383</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>363.2771476844816</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>15857304.347766038</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3894133.971455816</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2455735152743297</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.24557351527432958</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>7395.7483718106</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7484994608154554</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>560.4017216147629</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>7395.7483718106</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>590.4464335200166</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$101,A10,'Species'!$U$2:$U$101))</x:f>
-        <x:v>4366793.249347039</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7484994608154554</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>560.4017216147629</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4144590.1201922395</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>222203.12915479904</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0536128115714594</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.05361281157145946</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9905.680781111801</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.031289497754129</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1074.7055650592179</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9905.680781111801</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1322.0794169479568</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$101,A11,'Species'!$U$2:$U$101))</x:f>
-        <x:v>13096096.671564871</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.031289497754129</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1074.7055650592179</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>10645690.261160994</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2450406.4104038775</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2301782552648344</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.23017825526483446</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>11175.542165986799</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.337321525054145</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2174.3103094174826</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>11175.542165986799</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2227.264510465384</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$101,A12,'Species'!$U$2:$U$101))</x:f>
-        <x:v>24890888.451511845</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.337321525054145</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2174.3103094174826</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>24299096.544834882</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>591791.906676963</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0243544818872188</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.024354481887218837</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaa4517c88584c94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cd5b5ad349841cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8088,20 +7603,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8109,1038 +7614,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>8171.723878149601</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9866125387397213</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>969.6445007512474</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>8171.723878149601</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>982.3892704739786</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$101,A2,'Species'!$U$2:$U$101))</x:f>
-        <x:v>8027813.859170178</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9866125387397213</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>969.6445007512474</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>7923667.1201054165</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>104146.73906476144</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0131437549667504</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.013143754966750278</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>19523.417454574</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.339984130466746</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2187.6816825204783</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>19523.417454574</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2458.1139203513703</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$101,A3,'Species'!$U$2:$U$101))</x:f>
-        <x:v>47990784.21791927</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.339984130466746</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2187.6816825204783</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>42711022.74557212</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>5279761.472347148</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1236158989635645</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.12361589896356448</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>8631.5693027184</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.683677767420778</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>482.7005208317359</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>8631.5693027184</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>530.5744073909955</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$101,A4,'Species'!$U$2:$U$101))</x:f>
-        <x:v>4579689.767644123</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.683677767420778</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>482.7005208317359</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>4166462.9980173954</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>413226.7696267278</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0991792726404532</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.09917927264045333</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5.04</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5599999999999996</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>363.078054770101</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5.04</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>363.0780547701014</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$101,A5,'Species'!$U$2:$U$101))</x:f>
-        <x:v>1829.913396041311</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5599999999999996</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>363.078054770101</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1829.9133960413092</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1.8189894035458565e-12</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>9.94030322681344e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>11726.762806634099</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.346329049759447</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2219.877706593731</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>11726.762806634099</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2281.507217046095</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$101,A6,'Species'!$U$2:$U$101))</x:f>
-        <x:v>26754693.975923415</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.346329049759447</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2219.877706593731</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>26031979.32495957</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>722714.6509638466</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0277625701043371</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0277625701043372</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6065.013846708901</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.2345775560102</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1716.2381673895231</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6065.013846708901</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1816.4131932756866</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$101,A7,'Species'!$U$2:$U$101))</x:f>
-        <x:v>11016571.16856177</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.2345775560102</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1716.2381673895231</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>10409008.249467766</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>607562.9190940037</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.058368953557614</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.05836895355761387</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1873.7038707932002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>2.6076898372150312</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>40.52190342911374</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1873.7038707932002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>41.27976138065283</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$101,A8,'Species'!$U$2:$U$101))</x:f>
-        <x:v>77346.04868434886</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>2.6076898372150312</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>40.52190342911374</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>75926.04730703867</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1420.0013773101964</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.018702427265413</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.01870242726541299</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>137720.4968371792</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.268285711268527</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1854.7514158104455</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>137720.4968371792</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1874.3863711740057</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$101,A9,'Species'!$U$2:$U$101))</x:f>
-        <x:v>258141422.30292147</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.268285711268527</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1854.7514158104455</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>255437286.49487612</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2704135.8080453575</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0105863002428175</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.010586300242817528</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1866.28</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.066569646569646</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1165.653968457431</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1866.28</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1180.2775008306328</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$101,A10,'Species'!$U$2:$U$101))</x:f>
-        <x:v>2202728.2942501935</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.066569646569646</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1165.653968457431</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2175436.688252734</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>27291.605997459497</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0125453460194145</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.012545346019414406</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3863.301670313</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.357804568824785</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>227.9316155959386</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3863.301670313</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>260.54170922601395</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$101,A11,'Species'!$U$2:$U$101))</x:f>
-        <x:v>1006551.2204390636</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.357804568824785</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>227.9316155959386</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>880568.5912489303</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>125982.6291901333</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1430696375525378</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.14306963755253785</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>34712.2258825113</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.6832642966790563</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>482.2411837358313</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>34712.2258825113</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>962.2639638571363</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$101,A12,'Species'!$U$2:$U$101))</x:f>
-        <x:v>33402324.07200961</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.6832642966790563</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>482.2411837358313</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>16739664.899687812</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>16662659.172321796</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.9953998047256338</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.9953998047256339</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>28114.784101299603</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.358305640332869</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>228.19474569302517</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>28114.784101299603</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>263.4643779587497</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$101,A13,'Species'!$U$2:$U$101))</x:f>
-        <x:v>7407244.104693446</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.358305640332869</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>228.19474569302517</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>6415646.00821037</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>991598.096483076</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.15455935305877</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.15455935305877014</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1212.3189415851</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.9432632115271025</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>87.75325034477225</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1212.3189415851</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>267.8740031894226</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$101,A14,'Species'!$U$2:$U$101))</x:f>
-        <x:v>324748.7280247645</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.9432632115271025</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>87.75325034477225</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>106384.92757862661</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>218363.8004461379</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>3.052582122451043</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>2.052582122451043</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1506.855868496</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.0183809829168524</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>10.432321989365464</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1506.855868496</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>10.558017593378262</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$101,A15,'Species'!$U$2:$U$101))</x:f>
-        <x:v>15909.41077026605</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.0183809829168524</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>10.432321989365464</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>15720.005611715216</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>189.40515855083322</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.012048669906942</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.012048669906942047</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>24.765712074</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.2400000000000007</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>173.78008287493782</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>24.765712074</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$101,A16,'Species'!$U$2:$U$101))</x:f>
-        <x:v>4303.787496676563</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.2400000000000007</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>173.78008287493782</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4303.7874966765685</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>-5.4569682106375694e-12</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>-1.2679455514129124e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>380123.5687762425</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.0514136257342024</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>112.56765674630027</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>380123.5687762425</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>119.28923616258545</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$101,A17,'Species'!$U$2:$U$101))</x:f>
-        <x:v>45344650.16671398</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.0514136257342024</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>112.56765674630027</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>42789619.41118273</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2555030.7555312514</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0597114625156847</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.05971146251568468</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>190.13000000000002</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>4.03</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>1071.519305237607</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>190.13000000000002</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>1071.519305237607</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$101,A18,'Species'!$U$2:$U$101))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>203727.96550482628</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>4.03</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>1071.519305237607</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>203727.96550482628</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>3840.6669344028996</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.7102658554409924</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>513.1754306494264</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>3840.6669344028996</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>541.4490604159623</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$101,A19,'Species'!$U$2:$U$101))</x:f>
-        <x:v>2079525.5030031044</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.7102658554409924</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>513.1754306494264</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1970935.9080432204</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>108589.59495988395</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0550954470496676</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.055095447049667685</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R958349d9adbc4a4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74479202368641d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9315,7 +8146,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9414,7 +8245,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>448581864.50712657</x:v>
+        <x:v>411561111.14749527</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9428,7 +8259,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>448581864.5071266</x:v>
+        <x:v>418059191.08651906</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9442,7 +8273,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>5.960464477539063e-8</x:v>
+        <x:v>-37020753.35963124</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9456,7 +8287,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-30522673.420607448</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9467,9 +8298,9 @@
         <x:v>EEZ_953</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9481,47 +8312,19 @@
         <x:v>EEZ_953</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_953</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_953</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8522c4bb4b34ecc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd47ccef78ab4025"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9568,7 +8371,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
